--- a/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 4.xlsx
+++ b/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\translator\TraductorBrailleEspanol\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A6AC60-CC9D-4B5C-A501-BF144F943F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857B94EF-1DFA-4D52-AF3C-72C99FAFEACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
   </bookViews>
   <sheets>
     <sheet name="PR Formato" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="16">
   <si>
     <t>Reporte de Problema</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>El campo de entrada y salida de texto tiene un tamaño de fuente muy pequeño, a veces ilegible el resultado en braille.</t>
+  </si>
+  <si>
+    <t> El tamaño por Defecto de la fuente es el inadecuado en los campos de entrada y salida de texto, lo que dificulta la lectura, especialmente en la representación de caracteres Braille, comprometiendo la legibilidad y accesibilidad del contenido.</t>
+  </si>
+  <si>
+    <t> Aumentar el tamaño base de la fuente en los campos de entrada y salida, ajustándolo a un tamaño que sea claramente legible para todos los usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Realizar pruebas en diferentes resoluciones de pantalla y dispositivos para garantizar que el texto sea legible en todas las condiciones. </t>
   </si>
 </sst>
 </file>
@@ -317,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -381,6 +390,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,7 +744,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
   <dimension ref="B1:H28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -969,26 +996,26 @@
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
+      <c r="C18" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="19"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="9" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1053,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -1085,12 +1112,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
